--- a/Frameworks/MiniExcel/ImportQueryExcel/TestTypeMapping.xlsx
+++ b/Frameworks/MiniExcel/ImportQueryExcel/TestTypeMapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\aspnetcore-developer\Frameworks\MiniExcel\ImportQueryExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D30F3EB-2CF7-4AD0-A158-03EA726108EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90555930-3ECD-49B8-909C-00F624E14E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="401">
   <si>
     <t>ID</t>
   </si>
@@ -1220,10 +1220,6 @@
   </si>
   <si>
     <t>IgnoredProperty</t>
-  </si>
-  <si>
-    <t>BoD</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
@@ -1607,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>400</v>
+      </c>
+      <c r="C1" s="1">
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
